--- a/data/colleges/college_template.xlsx
+++ b/data/colleges/college_template.xlsx
@@ -700,7 +700,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fri 6-8</t>
+          <t>Fri 5-6</t>
         </is>
       </c>
     </row>
